--- a/OL-PROJECTS/al_construction_planner/static/examples/maestro_planificacion_ejemplo.xlsx
+++ b/OL-PROJECTS/al_construction_planner/static/examples/maestro_planificacion_ejemplo.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A72"/>
+  <dimension ref="A1:A95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -640,7 +640,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Familia: Cocina, Closet, Baño, Lavandería u Otro.</t>
+          <t xml:space="preserve">  Familia: Cocina, Closet, Baño, Lavandería, Ducto, Área común, Especial u Otro.</t>
         </is>
       </c>
     </row>
@@ -666,151 +666,151 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr"/>
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Variante de: Código de la tipología base de una variante con sufijo (03 para 03A).</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>MODULOS: Plantilla de módulos de cada tipología.</t>
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Otros nombres: Cómo se llama en la cotización, la orden o el ETO, separados por «;» (p. ej. «VK-01; V-K-01; COCINA 05»).</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Tipología *: Código de la tipología.</t>
-        </is>
-      </c>
+      <c r="A37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Orden: Orden del módulo en la tipología.</t>
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>MUEBLES: Muebles de cada tipología (con el nivel Mueble en la plantilla de la obra).</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Código del módulo *: MB01, MA01, CAMPANA… (el mismo del ETO).</t>
+          <t xml:space="preserve">  Tipología *: Código de la tipología.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Tipo *: Bajo, Alto, Cajonera, Campana, Repisero u Otro.</t>
+          <t xml:space="preserve">  Mueble *: Mueble bajo, mueble alto, torre de horno…</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Ancho (mm): Con ancho, las actividades por ML bajan al módulo.</t>
+          <t xml:space="preserve">  Grupo: Bajo, Alto u Otro.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Grupo ML: Mueble bajo, Mueble alto o Sin ML.</t>
+          <t xml:space="preserve">  Metros lineales: Sin anchos en los módulos, los ML del mueble.</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Actividad de armado *: Código de una actividad que se mide por módulo.</t>
-        </is>
-      </c>
+      <c r="A43" s="2" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr"/>
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>MODULOS: Plantilla de módulos de cada tipología.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="inlineStr">
-        <is>
-          <t>ACTIVIDADES: Actividades por ambiente de cada tipología.</t>
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Tipología *: Código de la tipología.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Tipología *: Código de la tipología.</t>
+          <t xml:space="preserve">  Orden: Orden del módulo en la tipología.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Actividad *: Código de la actividad.</t>
+          <t xml:space="preserve">  Código del módulo *: MB01, MA01, CAMPANA… (el mismo del ETO).</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Cantidad por ambiente *: Unidades de driver de un ambiente.</t>
+          <t xml:space="preserve">  Tipo *: Bajo, Alto, Cajonera, Campana, Repisero u Otro.</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr"/>
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Ancho (mm): Con ancho, las actividades por ML bajan al módulo.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="inlineStr">
-        <is>
-          <t>BOM: Lista de materiales de un ambiente de cada tipología.</t>
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Grupo ML: Mueble bajo, Mueble alto o Sin ML.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Tipología *: Código de la tipología.</t>
+          <t xml:space="preserve">  Actividad de armado *: Código de una actividad que se mide por módulo.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Código del producto *: Referencia interna del producto.</t>
+          <t xml:space="preserve">  Mueble: Mueble de la tipología al que pertenece (hoja MUEBLES).</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Producto: Nombre (para crear el producto si no existe).</t>
-        </is>
-      </c>
+      <c r="A53" s="2" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Cantidad *: Cantidad por ambiente.</t>
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>ACTIVIDADES: Actividades por ambiente de cada tipología.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Unidad: Unidad de la cantidad; vacía: la del producto.</t>
+          <t xml:space="preserve">  Tipología *: Código de la tipología.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Etapa de consumo: Producción, Armado, Instalación o Acabado y entrega. Sin etapa no se aprueba el plan.</t>
+          <t xml:space="preserve">  Actividad *: Código de la actividad.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Costo unitario: Costo del maestro: informativo y costo del producto si se crea.</t>
+          <t xml:space="preserve">  Cantidad por ambiente *: Unidades de driver de un ambiente.</t>
         </is>
       </c>
     </row>
@@ -820,92 +820,245 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>ARBOL: Árbol de la obra: piso › departamento › ambiente.</t>
+          <t>BOM: Lista de materiales de un ambiente de cada tipología.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Piso *: Nombre del piso.</t>
+          <t xml:space="preserve">  Tipología *: Código de la tipología.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Departamento *: Nombre del departamento.</t>
+          <t xml:space="preserve">  Código del producto *: Referencia interna del producto.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Ambiente *: Nombre del ambiente.</t>
+          <t xml:space="preserve">  Producto: Nombre (para crear el producto si no existe).</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Tipología: Código de la tipología del ambiente.</t>
+          <t xml:space="preserve">  Cantidad *: Cantidad por ambiente.</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="inlineStr"/>
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Unidad: Unidad de la cantidad; vacía: la del producto.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
-      <c r="A65" s="3" t="inlineStr">
-        <is>
-          <t>ETO: Módulos reales de cada ambiente (código y ancho), del despiece de ingeniería.</t>
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Etapa de consumo: Producción, Armado, Instalación o Acabado y entrega. Sin etapa no se aprueba el plan.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Piso *: Piso del ambiente.</t>
+          <t xml:space="preserve">  Costo unitario: Costo del maestro: informativo y costo del producto si se crea.</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Departamento *: Departamento del ambiente.</t>
-        </is>
-      </c>
+      <c r="A67" s="2" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Ambiente *: Ambiente.</t>
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>ARBOL: Árbol de la obra: agrupador › piso › unidad › ambiente.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Código del módulo *: El mismo código de la plantilla de la tipología.</t>
+          <t xml:space="preserve">  Agrupador: Torre o etapa encima del piso (p. ej. «Torre A»); varios niveles separados por « / » (p. ej. «Etapa 1 / Torre A»). Vacío si la obra no tiene agrupadores.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Tipo: Bajo, Alto, Cajonera, Campana, Repisero u Otro.</t>
+          <t xml:space="preserve">  Piso *: Nombre del piso.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Ancho (mm) *: Ancho real del módulo.</t>
+          <t xml:space="preserve">  Departamento *: Nombre del departamento.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Ambiente *: Nombre del ambiente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Tipología: Código de la tipología del ambiente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Tipo de unidad: Departamento, Nivel de dúplex, Ducto, Estacionamiento, Área común, Depósito, Local o Piloto. Vacío: Departamento.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>VARIANTES: Variantes de una unidad o ambiente frente a su tipología.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Agrupador: Torre o etapa, como en ÁRBOL.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Piso *: Piso de la unidad.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Departamento *: Unidad.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Ambiente: Vacío: todos los ambientes de la unidad.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Tipo *: Color, Excluir o Metrado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Código del producto *: Material de la tipología.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Reemplazar por: Solo para Color: código del material nuevo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Cantidad por ambiente: Solo para Metrado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Nota: Por qué (p. ej. «el cliente pidió Rovere»).</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="3" t="inlineStr">
+        <is>
+          <t>ETO: Módulos reales de cada ambiente (código y ancho), del despiece de ingeniería.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Agrupador: Torre o etapa del piso, como en ÁRBOL.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Piso *: Piso del ambiente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Departamento *: Departamento del ambiente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Ambiente *: Ambiente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Código del módulo *: El mismo código de la plantilla de la tipología.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Tipo: Bajo, Alto, Cajonera, Campana, Repisero u Otro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Ancho (mm) *: Ancho real del módulo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">  Grupo ML: Mueble bajo, Mueble alto o Sin ML.</t>
         </is>
@@ -1392,7 +1545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1401,6 +1554,8 @@
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1432,6 +1587,16 @@
       <c r="F1" s="4" t="inlineStr">
         <is>
           <t>ML alto</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Variante de</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Otros nombres</t>
         </is>
       </c>
     </row>
@@ -1514,7 +1679,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1524,6 +1689,7 @@
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1560,6 +1726,11 @@
       <c r="G1" s="4" t="inlineStr">
         <is>
           <t>Actividad de armado</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Mueble</t>
         </is>
       </c>
     </row>
@@ -3498,824 +3669,836 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D37"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
+          <t>Agrupador</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
           <t>Piso</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>Departamento</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>Ambiente</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="E1" s="4" t="inlineStr">
         <is>
           <t>Tipología</t>
         </is>
       </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de unidad</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Piso 01</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Dpto 101</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>C01</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Piso 01</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Dpto 101</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Closet dormitorio</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>CL01</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Piso 01</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Dpto 101</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Baño</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>B01</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Piso 01</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Dpto 102</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>C02</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Piso 01</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Dpto 102</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>Closet dormitorio</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>CL01</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Piso 01</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Dpto 102</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Baño</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>B01</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Piso 01</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Dpto 103</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>C01</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Piso 01</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Dpto 103</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>Closet dormitorio</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>CL01</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Piso 01</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Dpto 103</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>Baño</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>B01</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Piso 01</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Dpto 104</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>C02</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Piso 01</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Dpto 104</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>Closet dormitorio</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>CL01</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Piso 01</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Dpto 104</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>Baño</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>B01</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Piso 02</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Dpto 201</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>C01</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>Piso 02</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Dpto 201</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>Closet dormitorio</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>CL01</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>Piso 02</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Dpto 201</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>Baño</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>B01</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>Piso 02</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Dpto 202</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>C02</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>Piso 02</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Dpto 202</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>Closet dormitorio</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>CL01</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>Piso 02</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>Dpto 202</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>Baño</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>B01</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>Piso 02</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>Dpto 203</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>C01</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>Piso 02</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>Dpto 203</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>Closet dormitorio</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>CL01</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>Piso 02</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>Dpto 203</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>Baño</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>B01</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>Piso 02</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>Dpto 204</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>C02</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>Piso 02</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>Dpto 204</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>Closet dormitorio</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>CL01</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>Piso 02</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>Dpto 204</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>Baño</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>B01</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>Piso 03</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>Dpto 301</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>C01</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>Piso 03</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>Dpto 301</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>Closet dormitorio</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>CL01</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>Piso 03</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>Dpto 301</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>Baño</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>B01</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>Piso 03</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>Dpto 302</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>C02</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>Piso 03</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>Dpto 302</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>Closet dormitorio</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>CL01</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>Piso 03</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>Dpto 302</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>Baño</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>B01</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>Piso 03</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>Dpto 303</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>C01</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>Piso 03</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>Dpto 303</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>Closet dormitorio</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>CL01</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>Piso 03</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>Dpto 303</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>Baño</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>B01</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>Piso 03</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>Dpto 304</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>Cocina</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>C02</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>Piso 03</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>Dpto 304</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>Closet dormitorio</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>CL01</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>Piso 03</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>Dpto 304</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>Baño</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>B01</t>
         </is>
